--- a/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571</v>
+        <v>0.5714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8494</v>
+        <v>0.9162</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.45</v>
+        <v>0.875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9519</v>
+        <v>0.9824000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -792,31 +792,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7775</v>
+        <v>0.8138</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1012,75 +1012,75 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9471000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams is used to transmit data in near real-time, as data transmitted by producers is available in the stream in milliseconds.</t>
+          <t>The only component that interacts directly with the presentation layer is the Api Gateway module. This is because the Api Gateway microservices design pattern is followed. This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>C_05, Security</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_C01</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
+          <t>CF_M01_AU10</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7891</v>
+        <v>0.9167</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1088,74 +1088,72 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module, improving the scalability and availability of the system.</t>
+          <t>NestJS framework is used to develop the different services. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_03, C_04, Scalability</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19, AU_20, AU_21</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42, 44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD05</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1164,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1187,60 +1185,60 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9471000000000001</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. This pattern increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>TypeScript is used instead of JavaScript because it is the default language for NestJS and because, thanks to its static typing, it allows for the detection of errors at compile time.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>*CF_M01_C07</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AD06</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8477</v>
+        <v>0.9872</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1260,228 +1258,58 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NestJS allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>For the data transmission to be as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real-time.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>C_01</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_20, AU_21</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>*CF_M01_C11</t>
+          <t>CF_M01_C01</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8893</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.8603</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>AWS was chosen over other cloud services due to its low price and its previous use by the company, allowing the creation of scalable and highly available applications.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C_02, Scalability</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M01_AD05</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9585</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>TypeScript was chosen over JavaScript because it is the default language for NestJS and because, thanks to its static typing, it allows for error detection at compile time.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M01_AU34</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>46</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1494,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,36 +1365,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module. The system must be able to grow in capacity when the data volume increases. The system scales automatically as data increases.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>R_24, R_25, C_03, C_04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_12, AU_16, AU_18, AU_19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>38, 45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6716</v>
+        <v>0.7383999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AWS is used for infrastructure. It is the set of cloud computing services that allows the creation of scalable and highly available applications.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_02, C_04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6922</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,34 +1486,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7383999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>AD_02</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.6073</v>
+      <c r="G3" t="n">
+        <v>0.5786</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6587</v>
       </c>
     </row>
   </sheetData>
